--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Presidenti e scrutatori di seggio.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Presidenti e scrutatori di seggio.xlsx
@@ -301,7 +301,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">Puoi iscriverti all'albo presidenti o l'albo scrutatori per partecipare ai seggi del nostro Comune nelle prossime elezioni. 
+      <t xml:space="preserve">Puoi iscriverti all'albo presidenti o l'albo scrutatori per partecipare ai seggi del nostro Comune nelle prossime elezioni.
 Per iscriverti, </t>
     </r>
     <r>
@@ -319,7 +319,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">. 
+      <t xml:space="preserve">.
 La domanda è gratuita e può essere inoltrata dal </t>
     </r>
     <r>
@@ -354,7 +354,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">. Non è necessario rinnovarla ogni anno. 
+      <t xml:space="preserve">. Non è necessario rinnovarla ogni anno.
 Per ulteriori informazioni sul ruolo del presidente e scrutatore, [visita questo sito](URL).</t>
     </r>
   </si>
@@ -416,7 +416,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">  del </t>
+      <t xml:space="preserve"> del </t>
     </r>
     <r>
       <rPr>
@@ -488,7 +488,7 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
